--- a/pregenereated_results/s2/att_summary_survey.xlsx
+++ b/pregenereated_results/s2/att_summary_survey.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4117363946512974</v>
+        <v>0.4119231277135923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.03602010670634243</v>
+        <v>0.0355166202146675</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3411382827875765</v>
+        <v>0.3423118312402568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4823345065150182</v>
+        <v>0.4815344241869278</v>
       </c>
       <c r="G2" t="n">
-        <v>2.936035288108103e-30</v>
+        <v>4.216315028048566e-31</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4997581571589475</v>
+        <v>0.499321025741697</v>
       </c>
       <c r="I2" t="n">
-        <v>12.39377885716914</v>
+        <v>12.38111981572093</v>
       </c>
       <c r="J2" t="n">
         <v>3.79917864476386</v>
       </c>
       <c r="K2" t="n">
-        <v>3.380239265370626</v>
+        <v>3.380620028518701</v>
       </c>
       <c r="L2" t="n">
-        <v>9000</v>
+        <v>7220</v>
       </c>
       <c r="M2" t="n">
-        <v>541.114156846371</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="N2" t="n">
-        <v>8.80810586432431e-30</v>
+        <v>1.26489450841457e-30</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0462805685330589</v>
+        <v>-0.04579550992862588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -591,37 +591,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.03888357660028012</v>
+        <v>0.0390974269238337</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1224909782597123</v>
+        <v>-0.1224250585875266</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02992984119359454</v>
+        <v>0.03083403873027481</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2339542956047752</v>
+        <v>0.2414710814149033</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0436341156332072</v>
+        <v>-0.04256676218162161</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.286591398728017</v>
+        <v>-1.255616935124911</v>
       </c>
       <c r="J3" t="n">
         <v>3.137782340862423</v>
       </c>
       <c r="K3" t="n">
-        <v>3.178678950837071</v>
+        <v>3.177681852344856</v>
       </c>
       <c r="L3" t="n">
-        <v>9000</v>
+        <v>7220</v>
       </c>
       <c r="M3" t="n">
-        <v>541.114156846371</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2339542956047752</v>
+        <v>0.2414710814149033</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2588826584236549</v>
+        <v>0.2582177129441011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -648,37 +648,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03791786642415234</v>
+        <v>0.0379034316634053</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1845650058617157</v>
+        <v>0.1839283519933516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.333200310985594</v>
+        <v>0.3325070738948506</v>
       </c>
       <c r="G4" t="n">
-        <v>8.643213406854678e-12</v>
+        <v>9.590676754537563e-12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2955330927370888</v>
+        <v>0.2951129364911815</v>
       </c>
       <c r="I4" t="n">
-        <v>10.00018959366654</v>
+        <v>9.981897038554889</v>
       </c>
       <c r="J4" t="n">
         <v>3.061396303901438</v>
       </c>
       <c r="K4" t="n">
-        <v>2.783082752138914</v>
+        <v>2.783545643723753</v>
       </c>
       <c r="L4" t="n">
-        <v>9000</v>
+        <v>7220</v>
       </c>
       <c r="M4" t="n">
-        <v>541.114156846371</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="N4" t="n">
-        <v>1.296482011028202e-11</v>
+        <v>1.438601513180635e-11</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
